--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3710ADF-2BF1-4DDE-A801-A0AC465A8C52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{486CD890-9D3D-4537-A20C-61E8E3B3AA42}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13416350-0978-4A0A-AB62-C4029E82E8AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5825ADCA-E6BF-4F74-AE4E-FA7295E6AEB2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F633A24-637D-4DA6-9878-079ED73432B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D2C6A70-3A76-4461-BD0C-68D93591ABA9}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{486CD890-9D3D-4537-A20C-61E8E3B3AA42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30990379-0640-41C6-A33A-0C16AFB13ADB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5825ADCA-E6BF-4F74-AE4E-FA7295E6AEB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0099F76-C0AB-41D2-8C02-237083AC3DD6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D2C6A70-3A76-4461-BD0C-68D93591ABA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30454990-4D60-4CBC-A6C0-787E3712ED7A}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30990379-0640-41C6-A33A-0C16AFB13ADB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3710ADF-2BF1-4DDE-A801-A0AC465A8C52}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0099F76-C0AB-41D2-8C02-237083AC3DD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13416350-0978-4A0A-AB62-C4029E82E8AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30454990-4D60-4CBC-A6C0-787E3712ED7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F633A24-637D-4DA6-9878-079ED73432B0}"/>
 </file>